--- a/신고신저가_20260814.xlsx
+++ b/신고신저가_20260814.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,74 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 실버레이크의 워크데이 인수협상 보도가 SaaS 전반 재평가로 번지며 미국은 금융·소프트웨어 쌍끌이 신고가 확산, 중화권은 성장주 차익실현 — 디커플링 국면.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/13): S&amp;P500 +0.65%(7799, 52주위치 100)·나스닥 +0.81%. 신고가 109(NEW 60) vs 신저가 8(NEW 4). 순강도 금융 +35(유니버스 166 중)·테크서비스 +23·헬스테크 +13. ETF 1D 커뮤니케이션 +2.1%·리츠 +1.4%·필수소비재 +1.1%·테크 +1.0%. 워크데이 +17.8%(실버레이크 인수협상 로이터 보도, 변동성 정지)에 도큐사인·루브릭·세일포인트·클라우드플레어·뉴타닉스·몽고DB 동반 신고가 — 개별 실적이 아닌 SaaS 밸류에이션 바닥 재확인 성격. 금융 신규 신고가 PER(12MF) 중앙값 12.2배 vs 테크서비스 31.9배로 주도주 성격 이원화. 태피스트리 -16.5%(FY27 가이던스 부진).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/13): 신고가 13·신저가 0, 전부 OLD로 신규 돌파 없음. ETF 은행 +3.0%·전기정밀 +2.2%·기계 +2.0% vs 자동차 -1.1%·소매 -1.0%. 리소나·치바은행·스미토모미쓰이신탁·시즈오카 등 은행 4종 신고가 — 은행 ETF YTD26 +50.7%로 철강비철(+53.8%) 다음 2위. 어드밴테스트 +4.0%(PER 12MF 39.9배)·미쓰비시중공업 +4.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/13): 항셍 -0.17%·항셍테크 +0.33%. 신고가 8·신저가 2, 전부 OLD. 레노버 +20.2%(FY26/27 1Q 매출 43%↑·컨센 20% 상회, AI 매출 60%↑)가 단독 견인 — 미국 HP 신고가로 낙수 연결. 차오저우싼환 +9.0%(MLCC 가격인상 테마 추정). 헬스테크 3종 신고가(우시앱텍·팜아론·CSPC). 니오 신저가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/13): 상해종합 -0.50%·CSI300 -0.57%. 신고가 3·신저가 0. ETF 유색금속 -3.7%·부동산 -2.4%·태양광 -2.2%·반도체 -1.8%로 성장·소재 동반 조정, 백주 +0.7%·은행 +0.4%만 방어. 반도체 ETF 1M -13.3%이나 YTD26 +45.9%로 13개 중 1위 — 급등 후 되돌림 국면으로 판단. 루이제네트워크 +13.5%(알리바바클라우드 슈퍼노드 출시 수혜).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①실버레이크-워크데이 딜 성사 여부와 SaaS M&amp;A 프리미엄의 지속성 ②미 금융 신고가 35종의 폭이 실적 기반인지 금리 기대 기반인지 ③중국A 반도체·5G 1M 두 자릿수 조정의 저점 확인 여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 美는 8/13 ET 마감분(KST 8/14 05:00 종료, 약 2.7시간 전). 日 닛케이 지수값은 index CSV 기준 8/12분이라 종목 데이터(8/13)와 하루 어긋남. PER은 12개월 선행(TradingView) 기준이며 중국A는 표본이 얇아(전자기술 38/72) 절대 수준 인용 주의. 텔레그램 채널 적재분은 최신이 6/29로 낡아 이번 코멘트에 미반영.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +781,19 @@
       <c r="C2" t="n">
         <v>7798.99</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>2.99</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>4.77</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>13.93</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +819,19 @@
       <c r="C3" t="n">
         <v>26803.03</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>1.73</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>2.03</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>15.32</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +857,19 @@
       <c r="C4" t="n">
         <v>6579.04</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>3.68</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-0.29</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>-3.35</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-13.92</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>56.12</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +895,19 @@
       <c r="C5" t="n">
         <v>67524.06</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>5.58</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>-1.51</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>6.72</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>34.14</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +933,19 @@
       <c r="C6" t="n">
         <v>3926.96</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>-0.72</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-5.04</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-1.06</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +971,19 @@
       <c r="C7" t="n">
         <v>4663.95</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>-0.57</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-2.57</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-4.03</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.73</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1009,19 @@
       <c r="C8" t="n">
         <v>25396.51</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.17</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>-0.52</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>-3.76</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>-0.91</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1047,19 @@
       <c r="C9" t="n">
         <v>4792.39</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>-0.59</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-5.92</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-13.12</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1178,7 @@
       <c r="F2" t="n">
         <v>35</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1219,7 @@
       <c r="F3" t="n">
         <v>23</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1260,7 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1301,7 @@
       <c r="F5" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1342,7 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1383,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1424,7 @@
       <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1465,7 @@
       <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1506,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1547,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1588,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1629,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1670,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1711,7 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1680,7 +1752,7 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1721,7 +1793,7 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1762,7 +1834,7 @@
       <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1803,7 +1875,7 @@
       <c r="F19" t="n">
         <v>-1</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1844,7 +1916,7 @@
       <c r="F20" t="n">
         <v>-1</v>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1996,7 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2037,7 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2006,7 +2078,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2045,7 +2117,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2086,7 +2158,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2125,7 +2197,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2166,7 +2238,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2205,7 +2277,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2675,7 +2747,7 @@
       <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2716,7 +2788,7 @@
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2757,7 +2829,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2796,7 +2868,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2837,7 +2909,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2876,7 +2948,7 @@
       <c r="F46" t="n">
         <v>-1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2917,7 +2989,7 @@
       <c r="F47" t="n">
         <v>-1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3395,7 +3467,7 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3436,7 +3508,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3477,7 +3549,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -4101,30 +4173,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4218,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4328,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>테크 +1.0%, 워크데이 인수설발 SaaS 랠리가 견인. YTD26 +32.8%로 에너지 다음 2위</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4404,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>헬스케어 1D 보합이나 1M +6.4%·3M +15.3%, 헬스테크 순강도 +13으로 회복 지속</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4480,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>금융 +0.6%로 당일은 소폭이나 신고가 35종 최다. 신규 신고가군 PER 12MF 12.2배</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4556,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>경기소비재 +0.5%, 태피스트리 -16.5%에도 지수 방어. YTD26 -0.4%로 11개 중 10위</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4632,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>커뮤니케이션 +2.1%로 당일 1위. 다만 1M -0.7%·YTD26 -3.8% 최하위, 반등 성격 추정</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4708,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>산업재 -0.0% 보합, 순강도 +1로 중립. YTD26 +20.4%로 3위 유지</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4784,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>필수소비재 +1.1%, 매그넘아이스크림 등 방어주 수급 유입. 신고가 3종</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4860,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>에너지 1D 보합이나 1주 +5.0%·YTD26 +38.5%로 연간 1위 지속, 신고가 3종</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>38.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4936,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>유틸리티 +0.5%, 1M -2.6% 조정 중이나 신고가 1종 유지. YTD26 +4.5% 9위</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5012,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>소재 -0.5%로 당일 최하위, 순강도 +1. YTD26 +16.3%로 연간은 4위</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5088,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>리츠 +1.4%로 당일 2위, 금리 민감주 반등. YTD26 +13.6% 5위</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5164,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5236,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5308,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5380,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5452,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5524,63 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>자동차 -1.1%로 당일 최하위, YTD26 -2.3%로 16위. 신고가 종목 없음</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5600,63 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>철강·비철 +0.2%, YTD26 +53.8%로 일본 1위. 단 3M -11.9%로 최근 조정 국면</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>53.8</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5676,63 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>기계 +2.0%, 미쓰비시중공업 +4.0% 등 방산·중공업 강세. YTD26 +24.2% 6위</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5752,63 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>전기·정밀 +2.2%, 어드밴테스트 +4.0% 신고가 견인. YTD26 +39.7%로 3위</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>39.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5828,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5900,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5972,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>14</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6044,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6116,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6188,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>은행 +3.0%로 일본 17개 중 1위. 리소나·치바 등 4종 신고가, YTD26 +50.7% 2위</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6264,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6336,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6408,63 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>항셍지수 0.0% 보합, 3M -2.4%. 신고가 8·신저가 2로 방향성 부재</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6484,63 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>H주 -0.1%, 본토 약세 반영. YTD26 -5.0%로 홍콩 3종 중 중간</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6560,61 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>항셍테크 +0.5%, 레노버 +20.2% 견인. 단 YTD26 -12.7%로 홍콩 최하위</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-12.7</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6632,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>반도체 -1.8%, 1M -13.3% 조정 지속. 단 YTD26 +45.9%로 13개 중 1위, 급등 후 되돌림</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>45.9</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6708,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>테크 -1.0%, 1M -10.0%로 반도체와 동반 조정. YTD26 +32.4% 3위로 연간 강세는 유지</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>32.4</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6784,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>5G통신 -0.3%, 1M -12.8%로 성장주 조정 동참. YTD26 +37.7%로 2위</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>37.7</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6860,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>신에너지차 -1.1%, 3M -18.4%·YTD26 -11.2% 부진 지속. 홍콩 니오 신저가와 같은 방향</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-18.4</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-11.2</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6932,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>방산 -0.7%, 3M -17.1%·YTD26 -16.4%로 하위권. 신고가 종목 없음</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-16.4</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +7008,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>태양광 -2.2%, 3M -22.1%로 13개 중 최악. 공급과잉 부담 지속 추정</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-22.1</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-10.3</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7080,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>백주 +0.7%로 당일 상위, 1M +7.9%. 다만 YTD26 -16.2%로 소비 회복은 미확인</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-16.2</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>11</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7156,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>은행 +0.4%, 성장주 조정기 방어 수급 유입. 1M +1.6%로 상대 강세</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7232,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>유색금속 -3.7%로 당일 최하위, 1주 -2.5%. 1M +7.5%로 직전 급등분 되돌림 성격</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7308,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>부동산 -2.4%, YTD26 -17.3%로 13개 중 최하위. 반등 신호 미확인</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-17.3</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7384,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>증권 +0.4%, 지수 약세에도 방어. 1M -2.6%로 거래대금 둔화 반영 추정</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.1</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7460,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>의약 보합(0.0%), 1주 +5.8%·3M +12.6% 순환매 유입. 팜아론 A주 신고가와 정합</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7536,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>소비 +0.1%, 1M +4.3%로 완만한 회복. YTD26 -13.7%로 절대 수준은 여전히 부진</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7604,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3.7"/>
@@ -7366,7 +7616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-2.5"/>
@@ -7378,7 +7628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-13.3"/>
@@ -7390,7 +7640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-22.1"/>
@@ -7402,7 +7652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-17.3"/>
@@ -7414,7 +7664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7724,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,7 +7838,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7641,10 +7891,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7697,15 +7947,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7749,15 +7999,15 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7805,10 +8055,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7861,19 +8111,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 팔로알토네트웍스(기업 보안SW): 오펜하이머·바클레이스 목표가 상향+AI에이전트 해킹 보도로 보안주 랠리</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7919,15 +8169,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7971,15 +8221,15 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8023,10 +8273,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8075,10 +8325,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8127,10 +8377,10 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8183,10 +8433,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8235,15 +8485,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8287,15 +8537,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8343,15 +8593,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8397,15 +8647,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8451,10 +8701,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8503,15 +8753,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8559,15 +8809,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8615,10 +8865,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8667,10 +8917,10 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8723,10 +8973,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8779,10 +9029,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8835,10 +9085,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8891,10 +9141,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8943,15 +9193,15 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8995,15 +9245,15 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9047,15 +9297,15 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9103,15 +9353,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9155,10 +9405,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9211,15 +9461,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9267,10 +9517,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9315,10 +9565,10 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9371,15 +9621,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9423,15 +9673,15 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9475,15 +9725,15 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9527,15 +9777,15 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9579,15 +9829,19 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>워크데이(기업용 HR·재무 SaaS): 실버레이크 인수협상 로이터 보도, 변동성 정지 후 급등</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9635,10 +9889,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9687,15 +9941,15 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9739,15 +9993,15 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9793,15 +10047,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9845,10 +10099,10 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9893,14 +10147,14 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr">
+      <c r="N44" s="10" t="inlineStr">
         <is>
           <t>(전일) 아틀라시안(협업SW Jira·Confluence): 2분기 매출 28%↑·클라우드 31% 가속, Rovo AI 견인</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9949,10 +10203,10 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10005,10 +10259,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10061,10 +10315,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10117,14 +10371,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr">
+      <c r="N48" s="10" t="inlineStr">
         <is>
           <t>(전일) 에버퓨어(올플래시 데이터 스토리지): 서스퀘하나 투자의견 상향, AI·클라우드 플래시 수요 부각</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10175,15 +10429,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>몽고DB(NoSQL 데이터베이스 SaaS): RBC·오펜하이머 목표가 대폭 상향, Atlas 성장 기대</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10231,15 +10489,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10287,10 +10545,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10343,15 +10601,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10395,15 +10653,15 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10447,10 +10705,10 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10497,10 +10755,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10549,10 +10807,10 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10601,15 +10859,15 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10655,10 +10913,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>HP(PC·프린터 제조): 레노버 어닝서프라이즈 낙수, 골드만 Buy 신규·모간스탠리 상향</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10711,15 +10973,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10763,15 +11025,15 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10819,15 +11081,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10871,15 +11133,15 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10927,15 +11189,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10979,10 +11241,14 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>태피스트리(코치·케이트스페이드 핸드백): 4Q 서프라이즈에도 FY27 매출 가이던스 부진에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11031,10 +11297,10 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11083,10 +11349,10 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11139,19 +11405,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>(전일) 다든레스토랑츠(올리브가든 등 외식체인): 연속 강세 지속(신규 촉매 미확인, 외식업종 동반 강세 추정)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11199,15 +11465,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="7" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>글로벌페이먼츠(가맹점 결제처리): 모간스탠리·울프리서치 목표가·투자의견 상향에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11255,15 +11525,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11307,10 +11577,10 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11359,14 +11629,14 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>(전일) 텍사스퍼시픽랜드(퍼미안분지 토지·로열티 보유): 특별한 뉴스 없음(에너지 섹터 수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11419,15 +11689,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N72" s="7" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11475,15 +11745,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11527,10 +11797,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>루브릭(데이터 백업·랜섬웨어 복구 SW): 보안·SW 랠리, BTIG 목표가 109달러 상향 여진</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11583,14 +11857,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="7" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>(전일) 테넷헬스케어(병원·외래수술센터 운영): 2분기 서프라이즈·가이던스 상향 여파로 강세 지속, 신고가</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11639,10 +11913,14 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>TPG(대체투자 운용사): 개별 뉴스 없음, 워크데이 인수설발 PE 딜 훈풍 추정</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11689,10 +11967,10 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11741,15 +12019,15 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11793,15 +12071,15 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11845,10 +12123,14 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>아머스포츠(아크테릭스·살로몬 아웃도어): 8/18 실적 앞두고 내부자 매도·매출 우려로 신저가권</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11897,15 +12179,15 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11953,15 +12235,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12003,15 +12285,15 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12055,10 +12337,10 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12111,14 +12393,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>(전일) 제임스하디(파이버시멘트 건축자재): FY27 1분기 EBITDA 가이던스 상회, AZEK 통합 기대</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12171,19 +12453,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N86" s="7" t="inlineStr">
+      <c r="N86" s="10" t="inlineStr">
         <is>
           <t>(전일) 롤린스(해충방제 서비스): 2분기 EPS 0.32달러로 컨센 하회·경영진 교체 우려로 52주 신저가</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12227,15 +12509,15 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" s="7" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12277,15 +12559,15 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="7" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12333,15 +12615,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N89" s="7" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12389,10 +12671,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N90" s="7" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12445,10 +12727,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N91" s="7" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12497,15 +12779,15 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="7" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12549,15 +12831,19 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="7" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>뉴로크린(신경정신질환 신약 개발): 프래더윌리 치료제 Vykat 사망사례 안전성 우려 보도</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12601,15 +12887,15 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" s="7" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12653,10 +12939,10 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" s="7" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12705,15 +12991,15 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="7" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12761,15 +13047,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N97" s="7" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12813,15 +13099,15 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" s="7" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12865,10 +13151,10 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" s="7" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12921,14 +13207,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr">
+      <c r="N100" s="10" t="inlineStr">
         <is>
           <t>(전일) 무그(항공우주·방산 정밀제어시스템): 3분기 실적 호조·FY26 매출 가이던스 44억달러로 상향</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12981,15 +13267,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N101" s="7" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13033,15 +13319,15 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="7" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13089,10 +13375,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13145,15 +13431,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N104" s="7" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13197,10 +13483,10 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" s="7" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13251,15 +13537,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="7" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr">
+        <is>
+          <t>매그넘아이스크림(유니레버서 분사한 아이스크림): 개별 뉴스 없음, JPM 상향 여진·방어주 수급</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13303,15 +13593,19 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="7" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>도큐사인(전자서명·계약관리 SaaS): 개별 뉴스 없이 소프트웨어 업종 전반 랠리에 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13359,10 +13653,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N108" s="7" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13411,15 +13705,15 @@
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" s="7" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13461,15 +13755,15 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="7" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13517,10 +13811,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N111" s="7" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13571,14 +13865,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N112" s="7" t="inlineStr">
+      <c r="N112" s="10" t="inlineStr">
         <is>
           <t>(전일) 글라우코스(녹내장·각막질환 의료기기): 2분기 매출 급증·2026년 가이던스 상향, 목표주가 잇단 상향</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13631,15 +13925,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N113" s="7" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13683,10 +13977,10 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="7" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13735,19 +14029,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N115" s="7" t="inlineStr">
+      <c r="N115" s="10" t="inlineStr">
         <is>
           <t>(전일) 프락시스정밀의학(신경질환 치료제 바이오텍): RBC·베어드 목표주가 상향, 2분기 실적 호조 지속</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13791,15 +14085,15 @@
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" s="7" t="inlineStr"/>
+      <c r="N116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13839,10 +14133,14 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" s="7" t="inlineStr"/>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>허트8(비트코인 채굴·데이터센터): 2분기 순손실 전환, 75억달러 확장 파이낸싱 부담</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13893,7 +14191,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N118" s="7" t="inlineStr">
+      <c r="N118" s="10" t="inlineStr">
         <is>
           <t>(전일) 브링커인터내셔널(칠리스 등 캐주얼다이닝 체인): 4분기 매출 서프라이즈·FY27 가이던스 상회로 급등</t>
         </is>
@@ -14003,7 +14301,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14050,10 +14348,10 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14106,14 +14404,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 어드반테스트(반도체 테스터 장비): AI 반도체 테스터 수요 급증·실적 상향으로 급등</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14166,14 +14464,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 리크루트(구인 플랫폼 인디드·HR): FY27.3 영업이익 7870억→9450억엔 상향, 1Q 영업이익 66%↑</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14220,14 +14518,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시중공업(중공업·방위산업): 방위비 증액 기대와 1분기 실적 호조 지속으로 상승</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14280,14 +14578,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14340,14 +14638,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 스미토모미쓰이트러스트그룹(신탁은행 지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14394,14 +14692,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14448,14 +14746,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) LY코퍼레이션(야후재팬·라인): 1분기 사상 최대 실적 + 1500억엔 자사주매입</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14504,10 +14802,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14560,14 +14858,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 지바은행(지방은행): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14620,10 +14918,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14670,10 +14968,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14726,7 +15024,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N14"/>
@@ -14832,7 +15130,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14883,14 +15181,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시앱텍(신약 위탁연구 CRO): 상반기 순이익 29% 증가 서프라이즈, CXO 급등 주도</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14943,14 +15241,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 레노버(PC·서버 세계 1위): FY26/27 1분기 매출 43%·조정순이익 176% 급증, AI서버 매출 사상 최고</t>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>레노버(PC·서버 제조): FY26/27 1분기 매출 43% 급증·컨센 20% 상회, AI 매출 60% 증가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14999,14 +15297,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 차오저우싼환(적층세라믹콘덴서 MLCC·세라믹부품): AI 인프라용 고급 MLCC 공급부족·가격인상 수혜</t>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>차오저우싼환(전자세라믹·MLCC 부품): 신규 촉매 미확인, MLCC 공급부족·가격인상 테마 지속 추정</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15057,14 +15355,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) CLP홀딩스(홍콩 최대 전력회사, 발전·송배전): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15109,14 +15407,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 갤럭시엔터테인먼트(마카오 카지노·리조트): 8월 마카오 카지노 매출 호조 전망에 외국계 매수의견 강화</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15167,10 +15465,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15219,14 +15517,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 스야오그룹(CSPC, 항생제·비타민C·혁신신약 제약사): 특별한 뉴스 없음(8/20 중간실적 앞둔 제약 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15277,14 +15575,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 중국철도건설(대형 인프라·철도 시공): 특별한 뉴스 없음(국유 건설섹터 수급 부진 추정)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15337,14 +15635,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 캉룽화청(신약 위탁연구 CRO): CXO 섹터 랠리 지속·실적 호조로 목표주가 상향 잇따름(개별 신규 촉매는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15389,7 +15687,7 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 니오(중국 프리미엄 전기차): 특별한 뉴스 없음(전기차 섹터 수급 약세 추정)</t>
         </is>
@@ -15499,7 +15797,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15552,14 +15850,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>(전일) 루이제네트워크(데이터센터 스위치·네트워크장비): AI연산 수요 급증에 국산화 대체 기대로 상한가</t>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>루이제네트워크(데이터센터용 네트워크 스위치): 알리바바클라우드 슈퍼노드 출시로 스위치 수요 기대</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15610,14 +15908,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 진왕전자(PCB 제조): AI서버·광모듈용 PCB 수요로 연일 급등 후 차익실현 매물, 신고가는 장중 터치</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15670,7 +15968,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 캉룽화청A(신약 위탁개발 CXO): 상반기 중국 기술수출 2배 급증·수주잔고 25%↑</t>
         </is>

--- a/신고신저가_20260814.xlsx
+++ b/신고신저가_20260814.xlsx
@@ -9829,11 +9829,7 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="10" t="inlineStr">
-        <is>
-          <t>워크데이(기업용 HR·재무 SaaS): 실버레이크 인수협상 로이터 보도, 변동성 정지 후 급등</t>
-        </is>
-      </c>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -10429,11 +10425,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr">
-        <is>
-          <t>몽고DB(NoSQL 데이터베이스 SaaS): RBC·오펜하이머 목표가 대폭 상향, Atlas 성장 기대</t>
-        </is>
-      </c>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10913,11 +10905,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="10" t="inlineStr">
-        <is>
-          <t>HP(PC·프린터 제조): 레노버 어닝서프라이즈 낙수, 골드만 Buy 신규·모간스탠리 상향</t>
-        </is>
-      </c>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -11241,11 +11229,7 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="10" t="inlineStr">
-        <is>
-          <t>태피스트리(코치·케이트스페이드 핸드백): 4Q 서프라이즈에도 FY27 매출 가이던스 부진에 급락</t>
-        </is>
-      </c>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -11465,11 +11449,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="10" t="inlineStr">
-        <is>
-          <t>글로벌페이먼츠(가맹점 결제처리): 모간스탠리·울프리서치 목표가·투자의견 상향에 신고가</t>
-        </is>
-      </c>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -11797,11 +11777,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>루브릭(데이터 백업·랜섬웨어 복구 SW): 보안·SW 랠리, BTIG 목표가 109달러 상향 여진</t>
-        </is>
-      </c>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -11913,11 +11889,7 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="10" t="inlineStr">
-        <is>
-          <t>TPG(대체투자 운용사): 개별 뉴스 없음, 워크데이 인수설발 PE 딜 훈풍 추정</t>
-        </is>
-      </c>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -12123,11 +12095,7 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="10" t="inlineStr">
-        <is>
-          <t>아머스포츠(아크테릭스·살로몬 아웃도어): 8/18 실적 앞두고 내부자 매도·매출 우려로 신저가권</t>
-        </is>
-      </c>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -12831,11 +12799,7 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr">
-        <is>
-          <t>뉴로크린(신경정신질환 신약 개발): 프래더윌리 치료제 Vykat 사망사례 안전성 우려 보도</t>
-        </is>
-      </c>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -13537,11 +13501,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="10" t="inlineStr">
-        <is>
-          <t>매그넘아이스크림(유니레버서 분사한 아이스크림): 개별 뉴스 없음, JPM 상향 여진·방어주 수급</t>
-        </is>
-      </c>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -13593,11 +13553,7 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="10" t="inlineStr">
-        <is>
-          <t>도큐사인(전자서명·계약관리 SaaS): 개별 뉴스 없이 소프트웨어 업종 전반 랠리에 동반 급등</t>
-        </is>
-      </c>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -14133,11 +14089,7 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" s="10" t="inlineStr">
-        <is>
-          <t>허트8(비트코인 채굴·데이터센터): 2분기 순손실 전환, 75억달러 확장 파이낸싱 부담</t>
-        </is>
-      </c>
+      <c r="N117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -14333,7 +14285,7 @@
         <v>0.58</v>
       </c>
       <c r="H2" t="n">
-        <v>160.7</v>
+        <v>160.8</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
@@ -15243,7 +15195,7 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>레노버(PC·서버 제조): FY26/27 1분기 매출 43% 급증·컨센 20% 상회, AI 매출 60% 증가</t>
+          <t>(전일) 레노버(PC·서버 세계 1위): FY26/27 1분기 매출 43%·조정순이익 176% 급증, AI서버 매출 사상 최고</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15251,7 @@
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>차오저우싼환(전자세라믹·MLCC 부품): 신규 촉매 미확인, MLCC 공급부족·가격인상 테마 지속 추정</t>
+          <t>(전일) 차오저우싼환(적층세라믹콘덴서 MLCC·세라믹부품): AI 인프라용 고급 MLCC 공급부족·가격인상 수혜</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15804,7 @@
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>루이제네트워크(데이터센터용 네트워크 스위치): 알리바바클라우드 슈퍼노드 출시로 스위치 수요 기대</t>
+          <t>(전일) 루이제네트워크(데이터센터 스위치·네트워크장비): AI연산 수요 급증에 국산화 대체 기대로 상한가</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260814.xlsx
+++ b/신고신저가_20260814.xlsx
@@ -678,7 +678,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ 참고: 美는 8/13 ET 마감분(KST 8/14 05:00 종료, 약 2.7시간 전). 日 닛케이 지수값은 index CSV 기준 8/12분이라 종목 데이터(8/13)와 하루 어긋남. PER은 12개월 선행(TradingView) 기준이며 중국A는 표본이 얇아(전자기술 38/72) 절대 수준 인용 주의. 텔레그램 채널 적재분은 최신이 6/29로 낡아 이번 코멘트에 미반영.</t>
+          <t>■ 참고: 美는 8/13 ET 마감분(KST 8/14 05:00 종료, 약 3시간 전). 日·홍콩·中은 8/13 현지 마감분으로 8/14 장은 미개장. 日 닛케이 지수값은 index CSV 기준 8/12분이라 종목 데이터(8/13)와 하루 어긋남. PER은 12개월 선행(TradingView) 기준이며 중국A는 표본이 얇아(전자기술 38/72) 절대 수준 인용 주의. 텔레그램 채널 적재분은 최신이 7/30으로 낡아 이번 코멘트에 미반영(FinanceVault pull도 자격증명 부재로 실패). 원격 대시보드는 push 실패로 8/10 이후 미갱신 — 로컬 index.html만 최신.</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,11 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="10" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>워크데이(기업용 HR·재무 SaaS): 실버레이크 인수협상 로이터 보도, 변동성 정지 후 급등</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -10425,7 +10429,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>몽고DB(NoSQL 데이터베이스 SaaS): RBC·오펜하이머 목표가 대폭 상향, Atlas 성장 기대</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10905,7 +10913,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="10" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>HP(PC·프린터 제조): 레노버 어닝서프라이즈 낙수, 골드만 Buy 신규·모간스탠리 상향</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -11229,7 +11241,11 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="10" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>태피스트리(코치·케이트스페이드 핸드백): 4Q 서프라이즈에도 FY27 매출 가이던스 부진에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -11449,7 +11465,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="10" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>글로벌페이먼츠(가맹점 결제처리): 모간스탠리·울프리서치 목표가·투자의견 상향에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -11777,7 +11797,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="10" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>루브릭(데이터 백업·랜섬웨어 복구 SW): 보안·SW 랠리, BTIG 목표가 109달러 상향 여진</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -11889,7 +11913,11 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="10" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>TPG(대체투자 운용사): 개별 뉴스 없음, 워크데이 인수설발 PE 딜 훈풍 추정</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -12095,7 +12123,11 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="10" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>아머스포츠(아크테릭스·살로몬 아웃도어): 8/18 실적 앞두고 내부자 매도·매출 우려로 신저가권</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -12799,7 +12831,11 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>뉴로크린(신경정신질환 신약 개발): 프래더윌리 치료제 Vykat 사망사례 안전성 우려 보도</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -13501,7 +13537,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="10" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr">
+        <is>
+          <t>매그넘아이스크림(유니레버서 분사한 아이스크림): 개별 뉴스 없음, JPM 상향 여진·방어주 수급</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -13553,7 +13593,11 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="10" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>도큐사인(전자서명·계약관리 SaaS): 개별 뉴스 없이 소프트웨어 업종 전반 랠리에 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -14089,7 +14133,11 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" s="10" t="inlineStr"/>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>허트8(비트코인 채굴·데이터센터): 2분기 순손실 전환, 75억달러 확장 파이낸싱 부담</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -15195,7 +15243,7 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>(전일) 레노버(PC·서버 세계 1위): FY26/27 1분기 매출 43%·조정순이익 176% 급증, AI서버 매출 사상 최고</t>
+          <t>레노버(PC·서버 제조): FY26/27 1분기 매출 43% 급증·컨센 20% 상회, AI 매출 60% 증가</t>
         </is>
       </c>
     </row>
@@ -15251,7 +15299,7 @@
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>(전일) 차오저우싼환(적층세라믹콘덴서 MLCC·세라믹부품): AI 인프라용 고급 MLCC 공급부족·가격인상 수혜</t>
+          <t>차오저우싼환(전자세라믹·MLCC 부품): 신규 촉매 미확인, MLCC 공급부족·가격인상 테마 지속 추정</t>
         </is>
       </c>
     </row>
@@ -15804,7 +15852,7 @@
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>(전일) 루이제네트워크(데이터센터 스위치·네트워크장비): AI연산 수요 급증에 국산화 대체 기대로 상한가</t>
+          <t>루이제네트워크(데이터센터용 네트워크 스위치): 알리바바클라우드 슈퍼노드 출시로 스위치 수요 기대</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260814.xlsx
+++ b/신고신저가_20260814.xlsx
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'섹터동향'!$A$1:$K$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미국'!$A$1:$N$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$N$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'일본'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'홍콩'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'중국A'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -542,23 +542,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -569,23 +569,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -596,23 +596,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -855,29 +855,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6579.04</v>
+        <v>6967.62</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>-0.29</v>
+        <v>2.26</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>11.33</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-3.35</v>
+        <v>-4.35</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-13.92</v>
+        <v>-12.7</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>56.12</v>
+        <v>65.34</v>
       </c>
       <c r="I4" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -893,29 +893,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67524.06</v>
+        <v>68713.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>-1.51</v>
+        <v>4.61</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1.43</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6.72</v>
+        <v>11.89</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>34.14</v>
+        <v>36.5</v>
       </c>
       <c r="I5" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -931,29 +931,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3926.96</v>
+        <v>3926.14</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-0.72</v>
+        <v>-0.02</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1.13</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-5.04</v>
+        <v>-4.97</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-1.06</v>
+        <v>-1.08</v>
       </c>
       <c r="I6" t="n">
         <v>45</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -969,29 +969,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4663.95</v>
+        <v>4662.2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.27</v>
+        <v>-0.04</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-2.57</v>
+        <v>-0.77</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-4.03</v>
+        <v>-3.54</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="n">
         <v>55</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1007,29 +1007,29 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25396.51</v>
+        <v>25159.92</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-0.17</v>
+        <v>-0.93</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.52</v>
+        <v>-1.98</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.9</v>
+        <v>0.61</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-3.76</v>
+        <v>-4.66</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-0.91</v>
+        <v>-1.84</v>
       </c>
       <c r="I8" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1045,29 +1045,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4792.39</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.33</v>
+        <v>4717.94</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-1.55</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1.09</v>
+        <v>-2.89</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-2.41</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-5.92</v>
+        <v>-7.06</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-13.12</v>
+        <v>-14.47</v>
       </c>
       <c r="I9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="I2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J2" t="n">
         <v>18.8</v>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
         <v>21</v>
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="I11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J11" t="n">
-        <v>23</v>
+        <v>21.6</v>
       </c>
       <c r="K11" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1603,7 +1603,7 @@
         <v>24.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="13">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="I18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18" t="n">
         <v>21.7</v>
@@ -1988,10 +1988,10 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="I22" t="n">
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="K22" t="n">
         <v>1.4</v>
@@ -2022,37 +2022,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>21.6</v>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>29.1</v>
+        <v>11.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -2063,11 +2061,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -2083,15 +2081,17 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>13.3</v>
+      </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>25.3</v>
+        <v>20.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -2102,34 +2102,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>26.4</v>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>34.4</v>
+        <v>26.1</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -2143,11 +2141,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -2165,13 +2163,13 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>21</v>
+        <v>14.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -2182,7 +2180,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2202,17 +2200,15 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>19.1</v>
+        <v>25.6</v>
       </c>
       <c r="K27" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -2223,11 +2219,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -2243,15 +2239,17 @@
           <t>강세</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>26.1</v>
+      </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>11.2</v>
+        <v>34.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="29">
@@ -2262,11 +2260,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -2284,13 +2282,13 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>20.7</v>
       </c>
       <c r="K29" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
@@ -2301,35 +2299,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>23</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>강세</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>21.5</v>
+      </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J30" t="n">
-        <v>23.6</v>
+        <v>29.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="31">
@@ -2340,11 +2340,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>14.5</v>
+        <v>23.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2379,11 +2379,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -2399,17 +2399,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>20</v>
+        <v>34.8</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="33">
@@ -2420,11 +2418,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -2442,13 +2440,13 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>25.3</v>
+        <v>18.8</v>
       </c>
       <c r="K33" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="34">
@@ -2459,7 +2457,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2484,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>34.8</v>
+        <v>7.6</v>
       </c>
       <c r="K34" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="35">
@@ -2498,11 +2496,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -2520,13 +2518,13 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="K35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2537,11 +2535,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -2562,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="37">
@@ -2576,11 +2574,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -2598,13 +2596,13 @@
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>12.4</v>
+        <v>13.7</v>
       </c>
       <c r="K37" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
@@ -2615,11 +2613,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2635,15 +2633,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>16.2</v>
+      </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
-        <v>6.5</v>
+        <v>19.1</v>
       </c>
       <c r="K38" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="39">
@@ -2654,11 +2654,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2676,13 +2676,13 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>13.7</v>
+        <v>25.5</v>
       </c>
       <c r="K39" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="40">
@@ -2693,11 +2693,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>25.6</v>
+        <v>11.9</v>
       </c>
       <c r="K40" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="41">
@@ -2732,20 +2732,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>32.4</v>
+        <v>23.2</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J41" t="n">
-        <v>35.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="42">
@@ -2773,20 +2773,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -2794,16 +2794,16 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>23.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>78.3</v>
+        <v>11.5</v>
       </c>
       <c r="K42" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2836,13 +2836,13 @@
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>15.6</v>
+        <v>8.5</v>
       </c>
       <c r="K43" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="44">
@@ -2853,37 +2853,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>약세</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>19</v>
+      </c>
+      <c r="I44" t="n">
         <v>6</v>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>강세</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>5</v>
-      </c>
       <c r="J44" t="n">
-        <v>15.7</v>
+        <v>12.5</v>
       </c>
       <c r="K44" t="n">
-        <v>8.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="45">
@@ -2894,24 +2894,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>강세</t>
+        <v>-1</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>8.5</v>
+        <v>3.7</v>
       </c>
       <c r="K45" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="46">
@@ -2933,37 +2933,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>약세</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>18.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>12.4</v>
+        <v>30.1</v>
       </c>
       <c r="K46" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="47">
@@ -2974,35 +2972,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>3.7</v>
+        <v>12.1</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -3013,11 +3011,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -3035,13 +3033,13 @@
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="K48" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="49">
@@ -3052,35 +3050,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>15</v>
+      </c>
+      <c r="I49" t="n">
         <v>5</v>
       </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="n">
-        <v>2</v>
-      </c>
       <c r="J49" t="n">
-        <v>11.9</v>
+        <v>15.7</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="50">
@@ -3116,10 +3116,10 @@
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="K50" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="51">
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="K52" t="n">
         <v>0.7</v>
@@ -3210,37 +3210,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C53" t="n">
+        <v>11</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I53" t="n">
         <v>10</v>
       </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I53" t="n">
-        <v>8</v>
-      </c>
       <c r="J53" t="n">
-        <v>15.4</v>
+        <v>34.8</v>
       </c>
       <c r="K53" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -3271,15 +3271,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>10</v>
+      </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>23.8</v>
+        <v>15.6</v>
       </c>
       <c r="K54" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="55">
@@ -3290,11 +3292,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -3310,17 +3312,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H55" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="K55" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="56">
@@ -3331,11 +3331,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -3351,15 +3351,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>13.8</v>
+      </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J56" t="n">
-        <v>21.7</v>
+        <v>24.6</v>
       </c>
       <c r="K56" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="57">
@@ -3370,11 +3372,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -3390,17 +3392,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>14.9</v>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>15.5</v>
+        <v>18.2</v>
       </c>
       <c r="K57" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="58">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -3432,16 +3432,16 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.9</v>
+        <v>14.8</v>
       </c>
       <c r="I58" t="n">
         <v>6</v>
       </c>
       <c r="J58" t="n">
-        <v>13.1</v>
+        <v>15.5</v>
       </c>
       <c r="K58" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="59">
@@ -3459,27 +3459,27 @@
         <v>72</v>
       </c>
       <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
       <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>강세</t>
+        <v>-1</v>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>37.1</v>
+        <v>36.3</v>
       </c>
       <c r="I59" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J59" t="n">
-        <v>82.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K59" t="n">
         <v>10.7</v>
@@ -3493,37 +3493,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>강세</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>31.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>10</v>
-      </c>
-      <c r="J60" t="n">
-        <v>44.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
-        <v>5.4</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="61">
@@ -3534,37 +3530,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>강세</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>54.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>52.2</v>
+        <v>17.6</v>
       </c>
       <c r="K61" t="n">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="62">
@@ -3575,11 +3569,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -3597,11 +3591,13 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="J62" t="n">
+        <v>14.8</v>
+      </c>
       <c r="K62" t="n">
-        <v>15.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="63">
@@ -3612,11 +3608,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3637,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>17</v>
+        <v>18.9</v>
       </c>
       <c r="K63" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="64">
@@ -3651,11 +3647,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3673,13 +3669,13 @@
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>15.1</v>
+        <v>27.7</v>
       </c>
       <c r="K64" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="65">
@@ -3690,11 +3686,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -3712,13 +3708,13 @@
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
-        <v>19.2</v>
+        <v>15.3</v>
       </c>
       <c r="K65" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="66">
@@ -3729,11 +3725,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3749,15 +3745,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>7.4</v>
+      </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J66" t="n">
-        <v>27.9</v>
+        <v>6.8</v>
       </c>
       <c r="K66" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="67">
@@ -3768,11 +3766,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Health Services</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3790,13 +3788,13 @@
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K67" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="68">
@@ -3807,11 +3805,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3828,16 +3826,16 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>7.3</v>
+        <v>30.5</v>
       </c>
       <c r="I68" t="n">
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>6.7</v>
+        <v>43.8</v>
       </c>
       <c r="K68" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="69">
@@ -3848,11 +3846,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Health Services</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3870,13 +3868,13 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>24.1</v>
+        <v>7.2</v>
       </c>
       <c r="K69" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="70">
@@ -3887,11 +3885,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3909,13 +3907,13 @@
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
-        <v>7.2</v>
+        <v>19.4</v>
       </c>
       <c r="K70" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="71">
@@ -3926,11 +3924,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3946,17 +3944,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H71" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>19.1</v>
+        <v>27.1</v>
       </c>
       <c r="K71" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -3967,35 +3963,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C72" t="n">
+        <v>50</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I72" t="n">
         <v>18</v>
       </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="n">
-        <v>1</v>
-      </c>
       <c r="J72" t="n">
-        <v>27</v>
+        <v>39.6</v>
       </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="73">
@@ -4006,11 +4004,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -4026,17 +4024,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" t="n">
-        <v>30.8</v>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>18</v>
-      </c>
-      <c r="J73" t="n">
-        <v>39.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4047,11 +4041,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -4067,13 +4061,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>50.4</v>
+      </c>
       <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>42.3</v>
+      </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -4148,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="K76" t="n">
         <v>1.6</v>
@@ -5166,19 +5164,19 @@
       </c>
       <c r="D13" s="8" t="inlineStr"/>
       <c r="E13" s="9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>10.4</v>
+        <v>11.7</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
@@ -5238,19 +5236,19 @@
       </c>
       <c r="D14" s="8" t="inlineStr"/>
       <c r="E14" s="9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>-2.4</v>
+        <v>-3.8</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="J14" t="n">
         <v>9</v>
@@ -5310,19 +5308,19 @@
       </c>
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="9" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>-3.6</v>
+        <v>-2.3</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>-5.2</v>
+        <v>-2.9</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J15" t="n">
         <v>11</v>
@@ -5382,19 +5380,19 @@
       </c>
       <c r="D16" s="8" t="inlineStr"/>
       <c r="E16" s="9" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -5454,22 +5452,22 @@
       </c>
       <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="9" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
@@ -5530,19 +5528,19 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>-2.3</v>
+        <v>-1</v>
       </c>
       <c r="J18" t="n">
         <v>16</v>
@@ -5606,19 +5604,19 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>2.9</v>
+        <v>6.7</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>-11.9</v>
+        <v>-7.5</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>53.8</v>
+        <v>53.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -5682,19 +5680,19 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2</v>
+        <v>-0.3</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>-0.6</v>
+        <v>2.3</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="J20" t="n">
         <v>6</v>
@@ -5758,19 +5756,19 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>12.5</v>
+        <v>15.2</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>39.7</v>
+        <v>41.5</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -5830,19 +5828,19 @@
       </c>
       <c r="D22" s="8" t="inlineStr"/>
       <c r="E22" s="9" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>14.1</v>
+        <v>16.2</v>
       </c>
       <c r="J22" t="n">
         <v>10</v>
@@ -5902,19 +5900,19 @@
       </c>
       <c r="D23" s="8" t="inlineStr"/>
       <c r="E23" s="9" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>-2</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>15</v>
@@ -5974,22 +5972,22 @@
       </c>
       <c r="D24" s="8" t="inlineStr"/>
       <c r="E24" s="9" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>19.9</v>
@@ -6046,16 +6044,16 @@
       </c>
       <c r="D25" s="8" t="inlineStr"/>
       <c r="E25" s="9" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>18.8</v>
@@ -6118,19 +6116,19 @@
       </c>
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="9" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="n">
         <v>12</v>
@@ -6194,19 +6192,19 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3</v>
+        <v>-0.1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -6266,19 +6264,19 @@
       </c>
       <c r="D28" s="8" t="inlineStr"/>
       <c r="E28" s="9" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>-0.6</v>
+        <v>-1.7</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>12.2</v>
+        <v>9.6</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>29.1</v>
+        <v>28.4</v>
       </c>
       <c r="J28" t="n">
         <v>4</v>
@@ -6338,19 +6336,19 @@
       </c>
       <c r="D29" s="8" t="inlineStr"/>
       <c r="E29" s="9" t="n">
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>-3.8</v>
+        <v>-4.6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>-7.6</v>
+        <v>-6.6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="J29" t="n">
         <v>17</v>
@@ -6414,55 +6412,55 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>-2.4</v>
+        <v>-3.4</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>27.4</v>
+        <v>32.8</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>17.9</v>
+        <v>24.8</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>-13.7</v>
+        <v>-11.9</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>-15.3</v>
+        <v>-14.4</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
       <c r="S30" s="9" t="n">
-        <v>-14.2</v>
+        <v>-13.5</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" s="9" t="n">
-        <v>-3.7</v>
+        <v>-1.2</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
@@ -6490,19 +6488,19 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>-0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>-0.9</v>
+        <v>-2.3</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>-4.7</v>
+        <v>-5.3</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-5</v>
+        <v>-5.8</v>
       </c>
       <c r="J31" t="n">
         <v>2</v>
@@ -6566,19 +6564,19 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.5</v>
+        <v>-1.6</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>-0.6</v>
+        <v>-2.9</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>1.2</v>
+        <v>-2.5</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>-5.7</v>
+        <v>-6.7</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>-12.7</v>
+        <v>-14.1</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -6593,7 +6591,7 @@
         <v>18.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
@@ -6638,19 +6636,19 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>-1.8</v>
+        <v>0.2</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>2</v>
+        <v>-1.2</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>-13.3</v>
+        <v>-7.7</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -6714,19 +6712,19 @@
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>-1</v>
+        <v>0.8</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>-10</v>
+        <v>-5.1</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>32.4</v>
+        <v>33.5</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -6790,19 +6788,19 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>-0.3</v>
+        <v>2.4</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>-12.8</v>
+        <v>-8.6</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>-5.7</v>
+        <v>-5.1</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>37.7</v>
+        <v>41</v>
       </c>
       <c r="J35" t="n">
         <v>2</v>
@@ -6866,19 +6864,19 @@
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>-18.4</v>
+        <v>-18.1</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>-11.2</v>
+        <v>-10.9</v>
       </c>
       <c r="J36" t="n">
         <v>9</v>
@@ -6938,22 +6936,22 @@
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>-0.7</v>
+        <v>0.2</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>-17.1</v>
+        <v>-16.4</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-16.4</v>
+        <v>-16.2</v>
       </c>
       <c r="J37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>31.8</v>
@@ -7014,22 +7012,22 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>-22.1</v>
+        <v>-21.4</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-10.3</v>
+        <v>-10.1</v>
       </c>
       <c r="J38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>27.1</v>
@@ -7086,22 +7084,22 @@
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>0.7</v>
+        <v>-2</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>7.9</v>
+        <v>4.8</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>-1.3</v>
+        <v>-2.4</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-16.2</v>
+        <v>-17.9</v>
       </c>
       <c r="J39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>-13</v>
@@ -7162,22 +7160,22 @@
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-2.4</v>
+        <v>-2.9</v>
       </c>
       <c r="J40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>10.8</v>
@@ -7210,7 +7208,7 @@
         <v>7</v>
       </c>
       <c r="U40" s="9" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="V40" t="n">
         <v>10</v>
@@ -7238,22 +7236,22 @@
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>-3.7</v>
+        <v>1.1</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>-2.5</v>
+        <v>-4.8</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>-8.300000000000001</v>
+        <v>-6</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>101.1</v>
@@ -7286,7 +7284,7 @@
         <v>3</v>
       </c>
       <c r="U41" s="9" t="n">
-        <v>43.2</v>
+        <v>41.8</v>
       </c>
       <c r="V41" t="n">
         <v>7</v>
@@ -7314,19 +7312,19 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>-2.4</v>
+        <v>-1.3</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="H42" s="9" t="n">
         <v>-13.5</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>-17.3</v>
+        <v>-18.3</v>
       </c>
       <c r="J42" t="n">
         <v>13</v>
@@ -7362,7 +7360,7 @@
         <v>11</v>
       </c>
       <c r="U42" s="9" t="n">
-        <v>-4.3</v>
+        <v>-6.6</v>
       </c>
       <c r="V42" t="n">
         <v>11</v>
@@ -7390,22 +7388,22 @@
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>-2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-9.1</v>
+        <v>-10.2</v>
       </c>
       <c r="J43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>3.5</v>
@@ -7466,19 +7464,19 @@
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>5.8</v>
+        <v>-0.5</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="J44" t="n">
         <v>4</v>
@@ -7514,7 +7512,7 @@
         <v>13</v>
       </c>
       <c r="U44" s="9" t="n">
-        <v>62.9</v>
+        <v>58.4</v>
       </c>
       <c r="V44" t="n">
         <v>4</v>
@@ -7542,19 +7540,19 @@
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>0.1</v>
+        <v>-1.5</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-13.7</v>
+        <v>-15</v>
       </c>
       <c r="J45" t="n">
         <v>10</v>
@@ -7590,7 +7588,7 @@
         <v>12</v>
       </c>
       <c r="U45" s="9" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V45" t="n">
         <v>2</v>
@@ -7607,9 +7605,9 @@
   <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="-3.7"/>
+        <cfvo type="num" val="-2"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="2.4"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7619,9 +7617,9 @@
   <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="num" val="-2.5"/>
+        <cfvo type="num" val="-4.8"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="6.1"/>
+        <cfvo type="num" val="7.6"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7631,9 +7629,9 @@
   <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="num" val="-13.3"/>
+        <cfvo type="num" val="-8.6"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="9.300000000000001"/>
+        <cfvo type="num" val="10"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7643,9 +7641,9 @@
   <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="-22.1"/>
+        <cfvo type="num" val="-21.4"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="24.1"/>
+        <cfvo type="num" val="23.5"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -7655,9 +7653,9 @@
   <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="num" val="-17.3"/>
+        <cfvo type="num" val="-18.3"/>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="53.8"/>
+        <cfvo type="num" val="53.1"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -8523,7 +8521,7 @@
         <v>137.3</v>
       </c>
       <c r="I14" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="J14" t="n">
         <v>78.90000000000001</v>
@@ -9335,7 +9333,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="J29" t="n">
         <v>31</v>
@@ -9829,11 +9827,7 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="10" t="inlineStr">
-        <is>
-          <t>워크데이(기업용 HR·재무 SaaS): 실버레이크 인수협상 로이터 보도, 변동성 정지 후 급등</t>
-        </is>
-      </c>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -10241,7 +10235,7 @@
         <v>40.6</v>
       </c>
       <c r="I46" t="n">
-        <v>26.9</v>
+        <v>27.6</v>
       </c>
       <c r="J46" t="n">
         <v>52.6</v>
@@ -10429,11 +10423,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr">
-        <is>
-          <t>몽고DB(NoSQL 데이터베이스 SaaS): RBC·오펜하이머 목표가 대폭 상향, Atlas 성장 기대</t>
-        </is>
-      </c>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10913,11 +10903,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="10" t="inlineStr">
-        <is>
-          <t>HP(PC·프린터 제조): 레노버 어닝서프라이즈 낙수, 골드만 Buy 신규·모간스탠리 상향</t>
-        </is>
-      </c>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -11227,25 +11213,19 @@
         <v>25.9</v>
       </c>
       <c r="I64" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="J64" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="K64" t="n">
-        <v>38.1</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="10" t="inlineStr">
-        <is>
-          <t>태피스트리(코치·케이트스페이드 핸드백): 4Q 서프라이즈에도 FY27 매출 가이던스 부진에 급락</t>
-        </is>
-      </c>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -11465,11 +11445,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="10" t="inlineStr">
-        <is>
-          <t>글로벌페이먼츠(가맹점 결제처리): 모간스탠리·울프리서치 목표가·투자의견 상향에 신고가</t>
-        </is>
-      </c>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -11797,11 +11773,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>루브릭(데이터 백업·랜섬웨어 복구 SW): 보안·SW 랠리, BTIG 목표가 109달러 상향 여진</t>
-        </is>
-      </c>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -11913,11 +11885,7 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="10" t="inlineStr">
-        <is>
-          <t>TPG(대체투자 운용사): 개별 뉴스 없음, 워크데이 인수설발 PE 딜 훈풍 추정</t>
-        </is>
-      </c>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -12123,11 +12091,7 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="10" t="inlineStr">
-        <is>
-          <t>아머스포츠(아크테릭스·살로몬 아웃도어): 8/18 실적 앞두고 내부자 매도·매출 우려로 신저가권</t>
-        </is>
-      </c>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -12547,7 +12511,7 @@
         <v>16.6</v>
       </c>
       <c r="I88" t="n">
-        <v>50.3</v>
+        <v>53.5</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="n">
@@ -12831,11 +12795,7 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr">
-        <is>
-          <t>뉴로크린(신경정신질환 신약 개발): 프래더윌리 치료제 Vykat 사망사례 안전성 우려 보도</t>
-        </is>
-      </c>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -13357,14 +13317,12 @@
         <v>13.2</v>
       </c>
       <c r="I103" t="n">
-        <v>30.5</v>
+        <v>29.7</v>
       </c>
       <c r="J103" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="K103" t="n">
-        <v>7.1</v>
-      </c>
+        <v>32.6</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>O</t>
@@ -13537,11 +13495,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="10" t="inlineStr">
-        <is>
-          <t>매그넘아이스크림(유니레버서 분사한 아이스크림): 개별 뉴스 없음, JPM 상향 여진·방어주 수급</t>
-        </is>
-      </c>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -13593,11 +13547,7 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="10" t="inlineStr">
-        <is>
-          <t>도큐사인(전자서명·계약관리 SaaS): 개별 뉴스 없이 소프트웨어 업종 전반 랠리에 동반 급등</t>
-        </is>
-      </c>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -14133,11 +14083,7 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" s="10" t="inlineStr">
-        <is>
-          <t>허트8(비트코인 채굴·데이터센터): 2분기 순손실 전환, 75억달러 확장 파이낸싱 부담</t>
-        </is>
-      </c>
+      <c r="N117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -14209,7 +14155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14327,17 +14273,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5702</v>
+        <v>5768</v>
       </c>
       <c r="G2" t="n">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
       <c r="H2" t="n">
-        <v>160.8</v>
+        <v>161</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.9</v>
@@ -14377,22 +14323,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35940</v>
+        <v>36850</v>
       </c>
       <c r="G3" t="n">
-        <v>4.02</v>
+        <v>2.53</v>
       </c>
       <c r="H3" t="n">
-        <v>151.1</v>
+        <v>151.4</v>
       </c>
       <c r="I3" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="J3" t="n">
-        <v>57</v>
+        <v>58.5</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -14416,43 +14362,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6098 JP Equity</t>
+          <t>8411 JP Equity</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recruit Holdings Co., Ltd.</t>
+          <t>Mizuho Financial Group, Inc.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16790</v>
+        <v>8645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.78</v>
+        <v>-1.48</v>
       </c>
       <c r="H4" t="n">
-        <v>141.8</v>
+        <v>130.2</v>
       </c>
       <c r="I4" t="n">
-        <v>32.3</v>
+        <v>14.1</v>
       </c>
       <c r="J4" t="n">
-        <v>41.1</v>
+        <v>15.4</v>
       </c>
       <c r="K4" t="n">
-        <v>13.2</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -14464,11 +14410,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 리크루트(구인 플랫폼 인디드·HR): FY27.3 영업이익 7870억→9450억엔 상향, 1Q 영업이익 66%↑</t>
-        </is>
-      </c>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -14497,13 +14439,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4256</v>
+        <v>4254</v>
       </c>
       <c r="G5" t="n">
-        <v>3.96</v>
+        <v>-0.05</v>
       </c>
       <c r="H5" t="n">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
@@ -14530,59 +14472,49 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8308 JP Equity</t>
+          <t>9432 JP Equity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Resona Holdings, Inc.</t>
+          <t>NTT Inc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2446.5</v>
+        <v>162.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.37</v>
+        <v>1.25</v>
       </c>
       <c r="H6" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16.4</v>
-      </c>
+        <v>84.8</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>20.6</v>
+        <v>12.7</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -14590,43 +14522,41 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8309 JP Equity</t>
+          <t>6752 JP Equity</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Trust Group, Inc.</t>
+          <t>Panasonic Holdings Corporation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1753</v>
+        <v>4736</v>
       </c>
       <c r="G7" t="n">
-        <v>2.82</v>
+        <v>1.22</v>
       </c>
       <c r="H7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>13.4</v>
-      </c>
+        <v>67.09999999999999</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>13.3</v>
+        <v>43.7</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -14638,11 +14568,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 스미토모미쓰이트러스트그룹(신탁은행 지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
-        </is>
-      </c>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -14650,41 +14576,43 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4543 JP Equity</t>
+          <t>7974 JP Equity</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Terumo Corporation</t>
+          <t>Nintendo Co., Ltd.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2620.5</v>
+        <v>8903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.85</v>
+        <v>6.94</v>
       </c>
       <c r="H8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>61.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>28.8</v>
+      </c>
       <c r="J8" t="n">
-        <v>23.5</v>
+        <v>21.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -14692,11 +14620,7 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
-        </is>
-      </c>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -14704,19 +14628,19 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4689 JP Equity</t>
+          <t>6701 JP Equity</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LY Corporation</t>
+          <t>NEC Corporation</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -14725,20 +14649,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>499.5</v>
+        <v>5153</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.04</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>41.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22.5</v>
+      </c>
       <c r="J9" t="n">
-        <v>17</v>
+        <v>22.8</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -14746,55 +14672,49 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>(전일) LY코퍼레이션(야후재팬·라인): 1분기 사상 최대 실적 + 1500억엔 자사주매입</t>
-        </is>
-      </c>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9104 JP Equity</t>
+          <t>6367 JP Equity</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mitsui O.S.K.Lines,Ltd.</t>
+          <t>DAIKIN INDUSTRIES, LTD.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6279</v>
+        <v>21290</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>-0.35</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>39.6</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>9.800000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -14817,12 +14737,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8331 JP Equity</t>
+          <t>8308 JP Equity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chiba Bank, Ltd.</t>
+          <t>Resona Holdings, Inc.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -14831,22 +14751,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2842</v>
+        <v>2453.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.46</v>
+        <v>0.29</v>
       </c>
       <c r="H11" t="n">
-        <v>11.8</v>
+        <v>33.9</v>
       </c>
       <c r="I11" t="n">
         <v>16.5</v>
       </c>
       <c r="J11" t="n">
-        <v>19.4</v>
+        <v>20.7</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -14860,7 +14780,7 @@
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>(전일) 지바은행(지방은행): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
+          <t>(전일) 리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
@@ -14877,12 +14797,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5831 JP Equity</t>
+          <t>8309 JP Equity</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shizuoka Financial Group, Inc.</t>
+          <t>Sumitomo Mitsui Trust Group, Inc.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -14891,22 +14811,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3480</v>
+        <v>1731.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.29</v>
+        <v>-1.23</v>
       </c>
       <c r="H12" t="n">
-        <v>11.6</v>
+        <v>29.9</v>
       </c>
       <c r="I12" t="n">
-        <v>15.5</v>
+        <v>13.2</v>
       </c>
       <c r="J12" t="n">
-        <v>18.5</v>
+        <v>13.1</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -14918,49 +14838,53 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="10" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 스미토모미쓰이트러스트그룹(신탁은행 지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9435 JP Equity</t>
+          <t>8802 JP Equity</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hikari Tsushin, Inc.</t>
+          <t>Mitsubishi Estate Company, Limited</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40430</v>
+        <v>3674</v>
       </c>
       <c r="G13" t="n">
-        <v>1.46</v>
+        <v>-0.73</v>
       </c>
       <c r="H13" t="n">
-        <v>10.7</v>
+        <v>27.5</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -14983,51 +14907,441 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4188 JP Equity</t>
+          <t>4543 JP Equity</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mitsubishi Chemical Group Corporation</t>
+          <t>Terumo Corporation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1227</v>
+        <v>2661</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H14" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>17.1</v>
-      </c>
+        <v>24.1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>33.5</v>
+        <v>23.9</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 테루모(의료기기·수액세트): FY27.3 영업이익 2245억→2575억엔 상향, 1Q 순이익 68%↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4689 JP Equity</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LY Corporation</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Technology Services</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>506</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>(전일) LY코퍼레이션(야후재팬·라인): 1분기 사상 최대 실적 + 1500억엔 자사주매입</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7936 JP Equity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Asics Corporation</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Consumer Non-Durables</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5203</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9101 JP Equity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nippon Yusen Kabushiki Kaisha</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>6390</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>9104 JP Equity</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mitsui O.S.K.Lines,Ltd.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>6465</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H18" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8331 JP Equity</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Chiba Bank, Ltd.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2839.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>(전일) 지바은행(지방은행): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OLD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5831 JP Equity</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Shizuoka Financial Group, Inc.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3525</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>신고가</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>9107 JP Equity</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kawasaki Kisen Kaisha, Ltd.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3032</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N14"/>
+  <autoFilter ref="A1:N21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15038,7 +15352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15142,35 +15456,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2359 HK Equity</t>
+          <t>992 HK Equity</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WuXi AppTec Co., Ltd. Class H</t>
+          <t>Lenovo Group Limited</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203.2</v>
+        <v>33.86</v>
       </c>
       <c r="G2" t="n">
-        <v>2.16</v>
+        <v>-2.98</v>
       </c>
       <c r="H2" t="n">
-        <v>69.7</v>
+        <v>55.2</v>
       </c>
       <c r="I2" t="n">
-        <v>23.9</v>
+        <v>14.3</v>
       </c>
       <c r="J2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.4</v>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>O</t>
@@ -15183,7 +15499,7 @@
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>(전일) 우시앱텍(신약 위탁연구 CRO): 상반기 순이익 29% 증가 서프라이즈, CXO 급등 주도</t>
+          <t>(전일) 레노버(PC·서버 세계 1위): FY26/27 1분기 매출 43%·조정순이익 176% 급증, AI서버 매출 사상 최고</t>
         </is>
       </c>
     </row>
@@ -15200,12 +15516,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>992 HK Equity</t>
+          <t>6951 HK Equity</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lenovo Group Limited</t>
+          <t>Chaozhou Three-Circle (Group) Co., Ltd. Class H</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15214,22 +15530,18 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34.9</v>
+        <v>127.6</v>
       </c>
       <c r="G3" t="n">
-        <v>20.18</v>
+        <v>-2.45</v>
       </c>
       <c r="H3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="I3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>32.2</v>
-      </c>
+        <v>37.4</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -15243,7 +15555,7 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>레노버(PC·서버 제조): FY26/27 1분기 매출 43% 급증·컨센 20% 상회, AI 매출 60% 증가</t>
+          <t>(전일) 차오저우싼환(적층세라믹콘덴서 MLCC·세라믹부품): AI 인프라용 고급 MLCC 공급부족·가격인상 수혜</t>
         </is>
       </c>
     </row>
@@ -15260,32 +15572,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6951 HK Equity</t>
+          <t>2 HK Equity</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Chaozhou Three-Circle (Group) Co., Ltd. Class H</t>
+          <t>CLP Holdings Limited</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>130.8</v>
+        <v>78.5</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>-0.19</v>
       </c>
       <c r="H4" t="n">
-        <v>37.4</v>
+        <v>25.1</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>18.3</v>
+      </c>
       <c r="K4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -15299,7 +15613,7 @@
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>차오저우싼환(전자세라믹·MLCC 부품): 신규 촉매 미확인, MLCC 공급부족·가격인상 테마 지속 추정</t>
+          <t>(전일) CLP홀딩스(홍콩 최대 전력회사, 발전·송배전): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
         </is>
       </c>
     </row>
@@ -15309,114 +15623,118 @@
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1308 HK Equity</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SITC International Holdings Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>OLD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2 HK Equity</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CLP Holdings Limited</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>78.65000000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="H5" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>(전일) CLP홀딩스(홍콩 최대 전력회사, 발전·송배전): 특별한 뉴스 없음(유틸리티 방어주 수급 흐름 추정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>27 HK Equity</t>
+          <t>1186 HK Equity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Galaxy Entertainment Group Limited</t>
+          <t>China Railway Construction Corporation Limited Class H</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34.94</v>
+        <v>4.51</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>19.1</v>
+        <v>11.6</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>(전일) 갤럭시엔터테인먼트(마카오 카지노·리조트): 8월 마카오 카지노 매출 호조 전망에 외국계 매수의견 강화</t>
+          <t>(전일) 중국철도건설(대형 인프라·철도 시공): 특별한 뉴스 없음(국유 건설섹터 수급 부진 추정)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -15426,275 +15744,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19 HK Equity</t>
+          <t>9866 HK Equity</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Swire Pacific Limited Class A</t>
+          <t>NIO Inc. Class A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>103.9</v>
+        <v>35.38</v>
       </c>
       <c r="G7" t="n">
-        <v>0.97</v>
+        <v>0.17</v>
       </c>
       <c r="H7" t="n">
-        <v>15.8</v>
+        <v>10.6</v>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>16</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>16.1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1093 HK Equity</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CSPC Pharmaceutical Group Limited</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Health Technology</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H8" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 스야오그룹(CSPC, 항생제·비타민C·혁신신약 제약사): 특별한 뉴스 없음(8/20 중간실적 앞둔 제약 수급 추정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1186 HK Equity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>China Railway Construction Corporation Limited Class H</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Industrial Services</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 중국철도건설(대형 인프라·철도 시공): 특별한 뉴스 없음(국유 건설섹터 수급 부진 추정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3759 HK Equity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pharmaron Beijing Co., Ltd. Class H</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Health Technology</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="H10" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 캉룽화청(신약 위탁연구 CRO): CXO 섹터 랠리 지속·실적 호조로 목표주가 상향 잇따름(개별 신규 촉매는 미확인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>신저가</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>9866 HK Equity</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NIO Inc. Class A</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Consumer Durables</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="H11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 니오(중국 프리미엄 전기차): 특별한 뉴스 없음(전기차 섹터 수급 약세 추정)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N11"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15705,7 +15795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15797,48 +15887,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OLD</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>신저가</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>301165 CH Equity</t>
+          <t>001232 CH Equity</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ruijie Networks Co., Ltd. Class A</t>
+          <t>SHENZHEN JLC TECHNOLOGY GROUP CO LT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>143.3</v>
+        <v>161.98</v>
       </c>
       <c r="G2" t="n">
-        <v>13.52</v>
+        <v>-3.17</v>
       </c>
       <c r="H2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>224.2</v>
-      </c>
+        <v>14.1</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>31.1</v>
+        <v>11.9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -15850,132 +15936,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>루이제네트워크(데이터센터용 네트워크 스위치): 알리바바클라우드 슈퍼노드 출시로 스위치 수요 기대</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>603228 CH Equity</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Shenzhen Kinwong Electronic Co., Ltd. Class A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Electronic Technology</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="H3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>81</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 진왕전자(PCB 제조): AI서버·광모듈용 PCB 수요로 연일 급등 후 차익실현 매물, 신고가는 장중 터치</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>신고가</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>OLD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>300759 CH Equity</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pharmaron Beijing Co., Ltd. Class A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Health Technology</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>(전일) 캉룽화청A(신약 위탁개발 CXO): 상반기 중국 기술수출 2배 급증·수주잔고 25%↑</t>
-        </is>
-      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/신고신저가_20260814.xlsx
+++ b/신고신저가_20260814.xlsx
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 실버레이크의 워크데이 인수협상 보도가 SaaS 전반 재평가로 번지며 미국은 금융·소프트웨어 쌍끌이 신고가 확산, 중화권은 성장주 차익실현 — 디커플링 국면.</t>
+          <t>💬 ■ 결론: 일본이 개별 실적 촉매로 신규 돌파 8종을 만들며 아시아 유일 강세, 중화권은 성장주 소외 지속 — 미국 SaaS·금융 랠리의 아시아 낙수가 일본에만 선택적으로 걸리는 차별화 국면.</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 美(8/13): S&amp;P500 +0.65%(7799, 52주위치 100)·나스닥 +0.81%. 신고가 109(NEW 60) vs 신저가 8(NEW 4). 순강도 금융 +35(유니버스 166 중)·테크서비스 +23·헬스테크 +13. ETF 1D 커뮤니케이션 +2.1%·리츠 +1.4%·필수소비재 +1.1%·테크 +1.0%. 워크데이 +17.8%(실버레이크 인수협상 로이터 보도, 변동성 정지)에 도큐사인·루브릭·세일포인트·클라우드플레어·뉴타닉스·몽고DB 동반 신고가 — 개별 실적이 아닌 SaaS 밸류에이션 바닥 재확인 성격. 금융 신규 신고가 PER(12MF) 중앙값 12.2배 vs 테크서비스 31.9배로 주도주 성격 이원화. 태피스트리 -16.5%(FY27 가이던스 부진).</t>
+          <t>■ 美(8/13): S&amp;P500 +0.65%(7799, 52주위치 100)·나스닥 +0.81%·다우 +0.13%. 신고가 109(NEW 60) vs 신저가 8(NEW 4). 순강도 금융 +35(신고35/신저0)·테크서비스 +23·헬스테크 +13. ETF 1D 커뮤니케이션 +2.1%·리츠 +1.4%·필수소비재 +1.1%·테크 +1.0%. 워크데이 +17.8%(실버레이크 인수협상 로이터 보도)에 도큐사인·루브릭·세일포인트·클라우드플레어·뉴타닉스 동반 신고가 — 개별 실적이 아닌 SaaS 밸류 바닥 재확인 성격. 금융 PER(12MF) 중앙값 15.5배 vs 테크서비스 23.9배로 주도주 이원화. 태피스트리 -16.5%(FY27 가이던스 부진).</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 日(8/13): 신고가 13·신저가 0, 전부 OLD로 신규 돌파 없음. ETF 은행 +3.0%·전기정밀 +2.2%·기계 +2.0% vs 자동차 -1.1%·소매 -1.0%. 리소나·치바은행·스미토모미쓰이신탁·시즈오카 등 은행 4종 신고가 — 은행 ETF YTD26 +50.7%로 철강비철(+53.8%) 다음 2위. 어드밴테스트 +4.0%(PER 12MF 39.9배)·미쓰비시중공업 +4.0%.</t>
+          <t>■ 日(8/14): 닛케이225 68714(+0.59%, 52주위치 88). 신고가 18(NEW 8) vs 신저가 2 — 전일 전종목 OLD였던 데서 신규 돌파 8종으로 폭 확대. 아식스 +9.2%(2Q 경상익 +48%, 연간 1650→1890억엔 상향·증배, 상장래 최고가)·닌텐도 +6.9%(인도네시아 스위치 발매 추진 보도, 4개월래 최고)·NEC +4.8%. 해운 3종 동반 신고가(가와사키기선 +4.4·상선미쓰이 +3.0·니혼유센 +2.9, 운수ETF +1.6%)이나 당일 개별뉴스는 미확인. NTT·파나소닉·미즈호까지 통신·가전·은행으로 확산. ETF YTD26 철강비철 +53.1%·은행 +50.5%·전기정밀 +41.5% 상위 구도는 유지. 신저는 미쓰비시지쇼(부동산ETF 1M -4.6%)·다이킨.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ 홍콩(8/13): 항셍 -0.17%·항셍테크 +0.33%. 신고가 8·신저가 2, 전부 OLD. 레노버 +20.2%(FY26/27 1Q 매출 43%↑·컨센 20% 상회, AI 매출 60%↑)가 단독 견인 — 미국 HP 신고가로 낙수 연결. 차오저우싼환 +9.0%(MLCC 가격인상 테마 추정). 헬스테크 3종 신고가(우시앱텍·팜아론·CSPC). 니오 신저가.</t>
+          <t>■ 홍콩(8/14): 항셍 25160(-0.93%)·항셍테크 4718(-1.55%, 52주위치 19). 신고가 4(NEW 1)·신저가 2(전부 OLD). 전일 급등했던 레노버 -3.0%·차오저우싼환 -2.5%로 되돌림. 신규는 SITC인터내셔널(아시아 역내 컨테이너 해운) 1종뿐 — 일본 해운 강세와 같은 축.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ 中(8/13): 상해종합 -0.50%·CSI300 -0.57%. 신고가 3·신저가 0. ETF 유색금속 -3.7%·부동산 -2.4%·태양광 -2.2%·반도체 -1.8%로 성장·소재 동반 조정, 백주 +0.7%·은행 +0.4%만 방어. 반도체 ETF 1M -13.3%이나 YTD26 +45.9%로 13개 중 1위 — 급등 후 되돌림 국면으로 판단. 루이제네트워크 +13.5%(알리바바클라우드 슈퍼노드 출시 수혜).</t>
+          <t>■ 中(8/14): 상해종합 3926(-0.02%)·CSI300 4662(-0.04%)로 보합. 신고가 0·신저가 1. ETF 5G통신 +2.4%·유색금속 +1.1%가 반등한 반면 백주 -2.0%·의약 -1.7%·소비 -1.5%로 내수 약세. 반도체 YTD26 +46.2%로 13개 중 1위지만 1M -7.7%로 되돌림 지속. 유일 신저 자리촹(PCB, 8/4 상장)은 상장 후 조정이라 52주 저가의 의미가 제한적.</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①실버레이크-워크데이 딜 성사 여부와 SaaS M&amp;A 프리미엄의 지속성 ②미 금융 신고가 35종의 폭이 실적 기반인지 금리 기대 기반인지 ③중국A 반도체·5G 1M 두 자릿수 조정의 저점 확인 여부</t>
+          <t>■ 체크: ①일본 신규 돌파 8종이 실적 기반(아식스·닌텐도)과 무촉매 수급(해운·NTT·파나소닉)으로 갈리는데 후자의 지속성 ②실버레이크-워크데이 딜 성사 여부와 SaaS M&amp;A 프리미엄 지속성 ③항셍테크 52주위치 19·중국 반도체 1M -7.7%의 저점 확인 여부</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ 참고: 美는 8/13 ET 마감분(KST 8/14 05:00 종료, 약 3시간 전). 日·홍콩·中은 8/13 현지 마감분으로 8/14 장은 미개장. 日 닛케이 지수값은 index CSV 기준 8/12분이라 종목 데이터(8/13)와 하루 어긋남. PER은 12개월 선행(TradingView) 기준이며 중국A는 표본이 얇아(전자기술 38/72) 절대 수준 인용 주의. 텔레그램 채널 적재분은 최신이 7/30으로 낡아 이번 코멘트에 미반영(FinanceVault pull도 자격증명 부재로 실패). 원격 대시보드는 push 실패로 8/10 이후 미갱신 — 로컬 index.html만 최신.</t>
+          <t>■ 참고: 이 산출물은 15:47 KST 오후 재실행분으로, 08:18 정규 아침 실행분을 덮어썼다(아침본은 _am_backup_20260814/에 보존). 美는 8/13 ET 마감분으로 아침 실행과 동일 세션이라 미국 종목 이유는 그대로 승계. 日은 8/14 15:00 JST 마감 확정분(아침본 대비 하루 갱신). 홍콩·中은 8/14 장중 스냅샷(홍콩 14:32 HKT·중국 14:47 CST 기준)으로 마감 미확정 — 등락률·신고저 판정이 종가와 달라질 수 있다. PER은 12개월 선행(TradingView) 기준이며 중국A는 표본이 얇아(전자기술 34/72) 절대 수준 인용 주의. 텔레그램 채널 적재분은 최신이 7/30으로 낡아 미반영(FinanceVault git pull도 자격증명 부재로 실패). 원격 대시보드는 push 실패로 미갱신 — 로컬 index.html만 최신.</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>테크 +1.0%, 워크데이 인수설발 SaaS 랠리가 견인. YTD26 +32.8%로 에너지 다음 2위</t>
+          <t>+1.0%, 1M +5.1·3M +8.0%. 테크서비스 순강도 +23(신고25/신저2)로 SaaS 재평가가 섹터 견인</t>
         </is>
       </c>
       <c r="E2" s="9" t="n">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>헬스케어 1D 보합이나 1M +6.4%·3M +15.3%, 헬스테크 순강도 +13으로 회복 지속</t>
+          <t>-0.0% 보합이나 3M +15.3%로 SPDR 11개 중 1위. 헬스테크 순강도 +13, 조용한 주도 섹터</t>
         </is>
       </c>
       <c r="E3" s="9" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>금융 +0.6%로 당일은 소폭이나 신고가 35종 최다. 신규 신고가군 PER 12MF 12.2배</t>
+          <t>+0.6%이나 순강도 +35로 전 섹터 1위(신고35/신저0). PER 12MF 15.5배로 폭에 비해 배수 부담 낮음</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>경기소비재 +0.5%, 태피스트리 -16.5%에도 지수 방어. YTD26 -0.4%로 11개 중 10위</t>
+          <t>+0.5%, 3M -0.0%로 제자리. 태피스트리 -16.5% 등 소비 개별 실적 편차 확대</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>커뮤니케이션 +2.1%로 당일 1위. 다만 1M -0.7%·YTD26 -3.8% 최하위, 반등 성격 추정</t>
+          <t>+2.1%로 당일 1위. 다만 1M -0.7·3M -3.4%로 추세 회복은 미확인, 하루 반등 성격 추정</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>산업재 -0.0% 보합, 순강도 +1로 중립. YTD26 +20.4%로 3위 유지</t>
+          <t>-0.0%, 순강도 +1로 중립. 3M +7.3%는 유지 중</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>필수소비재 +1.1%, 매그넘아이스크림 등 방어주 수급 유입. 신고가 3종</t>
+          <t>+1.1%, 1M +3.0%. 순강도 +3, 리스크 회피성 수급 유입 추정</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>에너지 1D 보합이나 1주 +5.0%·YTD26 +38.5%로 연간 1위 지속, 신고가 3종</t>
+          <t>0.0%이나 1주 +5.0·1M +8.1%로 두 구간 모두 1위. 에너지광물 PER 12MF 10.5배로 최저</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>유틸리티 +0.5%, 1M -2.6% 조정 중이나 신고가 1종 유지. YTD26 +4.5% 9위</t>
+          <t>+0.5%, 1M -2.6%로 부진. 순강도 +1에 그쳐 방어주 내 필수소비재에 밀림</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>소재 -0.5%로 당일 최하위, 순강도 +1. YTD26 +16.3%로 연간은 4위</t>
+          <t>-0.5%로 당일 최하위. 1M +3.6%는 유지, 비에너지광물 순강도 +1</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>리츠 +1.4%로 당일 2위, 금리 민감주 반등. YTD26 +13.6% 5위</t>
+          <t>+1.4%로 당일 2위. 3M +3.0%, 금리 기대 되돌림에 반응한 반등 추정</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -5450,7 +5450,11 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>-0.7%로 당일 최하위. 1M +5.9%는 유지, 하루 되돌림 성격</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>-0.7</v>
       </c>
@@ -5524,7 +5528,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>자동차 -1.1%로 당일 최하위, YTD26 -2.3%로 16위. 신고가 종목 없음</t>
+          <t>+1.4%, 1M +8.7%. 엔화 159엔대 약세가 수출채산성 지지 추정</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -5600,7 +5604,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>철강·비철 +0.2%, YTD26 +53.8%로 일본 1위. 단 3M -11.9%로 최근 조정 국면</t>
+          <t>-0.5%이나 YTD26 +53.1%로 17개 중 1위. 1주 +6.7%로 단기 재가속</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -5674,11 +5678,7 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>기계 +2.0%, 미쓰비시중공업 +4.0% 등 방산·중공업 강세. YTD26 +24.2% 6위</t>
-        </is>
-      </c>
+      <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="9" t="n">
         <v>-0.3</v>
       </c>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>전기·정밀 +2.2%, 어드밴테스트 +4.0% 신고가 견인. YTD26 +39.7%로 3위</t>
+          <t>+1.3%, 1주 +6.3%. YTD26 +41.5% 3위, 어드밴테스트 등 반도체장비 강세 지속</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -5826,7 +5826,11 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>+1.8%로 당일 1위. 3M +20.2%, NEC 신고가 등 IT서비스 실적 모멘텀</t>
+        </is>
+      </c>
       <c r="E22" s="9" t="n">
         <v>1.8</v>
       </c>
@@ -5970,7 +5974,11 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>+1.6%. 해운 3종(가와사키기선·니혼유센·상선미쓰이) 동반 신고가가 견인</t>
+        </is>
+      </c>
       <c r="E24" s="9" t="n">
         <v>1.6</v>
       </c>
@@ -6188,7 +6196,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>은행 +3.0%로 일본 17개 중 1위. 리소나·치바 등 4종 신고가, YTD26 +50.7% 2위</t>
+          <t>-0.1%로 숨고르기. YTD26 +50.5% 2위·3M +23.5%로 올해 주도 섹터 지위는 유지</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
@@ -6334,7 +6342,11 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>-0.5%, 1M -4.6%로 최하위권. 미쓰비시지쇼 신저가로 부동산 약세 확인</t>
+        </is>
+      </c>
       <c r="E29" s="9" t="n">
         <v>-0.5</v>
       </c>
@@ -6408,7 +6420,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>항셍지수 0.0% 보합, 3M -2.4%. 신고가 8·신저가 2로 방향성 부재</t>
+          <t>-0.9%. 항셍 25159(52주위치 47), 1주 -1.9%로 조정 지속</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
@@ -6484,7 +6496,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>H주 -0.1%, 본토 약세 반영. YTD26 -5.0%로 홍콩 3종 중 중간</t>
+          <t>-0.9%. 본토 성장주 약세와 동조, 3M -5.3%</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
@@ -6560,7 +6572,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>항셍테크 +0.5%, 레노버 +20.2% 견인. 단 YTD26 -12.7%로 홍콩 최하위</t>
+          <t>-1.6%로 홍콩 3개 중 최하위. YTD26 -14.5%·52주위치 19로 성장주 소외 심화</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
@@ -6632,7 +6644,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>반도체 -1.8%, 1M -13.3% 조정 지속. 단 YTD26 +45.9%로 13개 중 1위, 급등 후 되돌림</t>
+          <t>+0.2% 강보합. 1M -7.7%로 조정 중이나 YTD26 +46.2%로 13개 중 1위 — 급등 후 되돌림 국면</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
@@ -6708,7 +6720,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>테크 -1.0%, 1M -10.0%로 반도체와 동반 조정. YTD26 +32.4% 3위로 연간 강세는 유지</t>
+          <t>+0.8%, 1M -5.1%. YTD26 +33.5% 3위로 성장주 축은 유지되나 단기 모멘텀은 둔화</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
@@ -6784,7 +6796,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>5G통신 -0.3%, 1M -12.8%로 성장주 조정 동참. YTD26 +37.7%로 2위</t>
+          <t>+2.4%로 당일 1위 반등. 다만 1M -8.6%로 13개 중 최하위, 낙폭과대 되돌림 성격 추정</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
@@ -6860,7 +6872,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>신에너지차 -1.1%, 3M -18.4%·YTD26 -11.2% 부진 지속. 홍콩 니오 신저가와 같은 방향</t>
+          <t>+0.4%, 3M -18.1%. YTD26 -10.9%로 하위권, 반등 신호 미확인</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
@@ -6932,7 +6944,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>방산 -0.7%, 3M -17.1%·YTD26 -16.4%로 하위권. 신고가 종목 없음</t>
+          <t>+0.2%, 3M -16.4%·YTD26 -16.2%로 하위권 지속</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
@@ -7008,7 +7020,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>태양광 -2.2%, 3M -22.1%로 13개 중 최악. 공급과잉 부담 지속 추정</t>
+          <t>+0.2%, 3M -21.4%로 13개 중 최하위. 공급과잉 조정 지속 추정</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
@@ -7080,7 +7092,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>백주 +0.7%로 당일 상위, 1M +7.9%. 다만 YTD26 -16.2%로 소비 회복은 미확인</t>
+          <t>-2.0%로 당일 최하위. 1M +4.8%로 반등하던 흐름이 하루 되돌림</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
@@ -7156,7 +7168,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>은행 +0.4%, 성장주 조정기 방어 수급 유입. 1M +1.6%로 상대 강세</t>
+          <t>-0.5%, 3M +3.6%. 방어 역할이나 YTD26 -2.9%로 성장주 대비 열위</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
@@ -7232,7 +7244,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>유색금속 -3.7%로 당일 최하위, 1주 -2.5%. 1M +7.5%로 직전 급등분 되돌림 성격</t>
+          <t>+1.1%, 1M +9.5%로 1M 1위. 다만 1주 -4.8%로 변동성 큼</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
@@ -7308,7 +7320,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>부동산 -2.4%, YTD26 -17.3%로 13개 중 최하위. 반등 신호 미확인</t>
+          <t>-1.3%, 3M -13.5%·YTD26 -18.3%로 13개 중 최하위. 반등 근거 미확인</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
@@ -7384,7 +7396,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>증권 +0.4%, 지수 약세에도 방어. 1M -2.6%로 거래대금 둔화 반영 추정</t>
+          <t>-1.3%, YTD26 -10.2%. 거래대금 둔화 국면 추정</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
@@ -7460,7 +7472,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>의약 보합(0.0%), 1주 +5.8%·3M +12.6% 순환매 유입. 팜아론 A주 신고가와 정합</t>
+          <t>-1.7%로 약세이나 3M +12.9%로 13개 중 1위 — 중기 추세는 유지</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
@@ -7536,7 +7548,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>소비 +0.1%, 1M +4.3%로 완만한 회복. YTD26 -13.7%로 절대 수준은 여전히 부진</t>
+          <t>-1.5%, YTD26 -15.0%. 내수 소비 회복 신호 여전히 미확인</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
@@ -9827,7 +9839,11 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="10" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>워크데이(기업용 HR·재무 SaaS): 실버레이크 인수협상 로이터 보도, 변동성 정지 후 급등</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -10423,7 +10439,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="10" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>몽고DB(NoSQL 데이터베이스 SaaS): RBC·오펜하이머 목표가 대폭 상향, Atlas 성장 기대</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10903,7 +10923,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="10" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>HP(PC·프린터 제조): 레노버 어닝서프라이즈 낙수, 골드만 Buy 신규·모간스탠리 상향</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -11225,7 +11249,11 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="10" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>태피스트리(코치·케이트스페이드 핸드백): 4Q 서프라이즈에도 FY27 매출 가이던스 부진에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -11445,7 +11473,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="10" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>글로벌페이먼츠(가맹점 결제처리): 모간스탠리·울프리서치 목표가·투자의견 상향에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -11773,7 +11805,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="10" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr">
+        <is>
+          <t>루브릭(데이터 백업·랜섬웨어 복구 SW): 보안·SW 랠리, BTIG 목표가 109달러 상향 여진</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -11885,7 +11921,11 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="10" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>TPG(대체투자 운용사): 개별 뉴스 없음, 워크데이 인수설발 PE 딜 훈풍 추정</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -12091,7 +12131,11 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="10" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>아머스포츠(아크테릭스·살로몬 아웃도어): 8/18 실적 앞두고 내부자 매도·매출 우려로 신저가권</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -12795,7 +12839,11 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>뉴로크린(신경정신질환 신약 개발): 프래더윌리 치료제 Vykat 사망사례 안전성 우려 보도</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -13495,7 +13543,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="10" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr">
+        <is>
+          <t>매그넘아이스크림(유니레버서 분사한 아이스크림): 개별 뉴스 없음, JPM 상향 여진·방어주 수급</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -13547,7 +13599,11 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="10" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr">
+        <is>
+          <t>도큐사인(전자서명·계약관리 SaaS): 개별 뉴스 없이 소프트웨어 업종 전반 랠리에 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -14083,7 +14139,11 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" s="10" t="inlineStr"/>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>허트8(비트코인 채굴·데이터센터): 2분기 순손실 전환, 75억달러 확장 파이낸싱 부담</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -14410,7 +14470,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>미즈호FG(3대 메가뱅크): 당일 -1.5% 하락에도 장중 고가가 52주 신고가 터치, 은행 랠리 연장</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -14514,7 +14578,11 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>NTT(통신 1위): 개별 뉴스 없음, 금리·방어주 수급에 신고가 진입 추정</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -14568,7 +14636,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>파나소닉(가전·전장·전지): 개별 뉴스 없음, 엔약세·전기정밀 섹터 강세 동조 추정</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -14620,7 +14692,11 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>닌텐도(게임기·소프트웨어): 인도네시아 스위치·스위치2 발매 추진 보도(지지통신)로 4개월래 최고가</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -14672,7 +14748,11 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>NEC(IT서비스·통신장비): 당일 촉매 미확인, 1Q 순이익 +157%·가이던스 상향 모멘텀 연장 추정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -14722,7 +14802,11 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>다이킨(공조·에어컨): 8/4 1Q 순이익 -1.7% 발표 후 약세 지속, 당일 신규 악재는 없음</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -14892,7 +14976,11 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>미쓰비시지쇼(오피스 부동산 디벨로퍼): 특별한 뉴스 없음, 부동산 섹터 약세 수급 추정</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -15002,7 +15090,7 @@
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>(전일) LY코퍼레이션(야후재팬·라인): 1분기 사상 최대 실적 + 1500억엔 자사주매입</t>
+          <t>LY Corporation(포털·메신저·페이페이 핀테크): 신규 촉매 없음, 8월초 페이페이발 호실적 모멘텀 연장</t>
         </is>
       </c>
     </row>
@@ -15058,7 +15146,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="10" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>아식스(러닝화·스포츠용품): 2Q 경상이익 +48%, 연간 전망 1650→1890억엔 상향·증배, 상장래 최고가</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -15114,7 +15206,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="10" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>니혼유센(벌크·컨테이너 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -15338,7 +15434,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="10" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>가와사키기선(컨테이너선 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N21"/>
@@ -15671,7 +15771,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -15936,7 +16040,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>선전 자리촹(PCB·전자제조서비스, 8/4 상장): 개별 악재 없음, 상장 초기 급등 후 조정 지속 추정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N2"/>

--- a/신고신저가_20260814.xlsx
+++ b/신고신저가_20260814.xlsx
@@ -5162,7 +5162,11 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>+0.8%, 1M +8.0·3M +11.7%. 내수 방어 섹터 중 성과 상위</t>
+        </is>
+      </c>
       <c r="E13" s="9" t="n">
         <v>0.8</v>
       </c>
@@ -5234,7 +5238,11 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>+0.6%, 1M +9.4%로 상위. 다만 3M -3.8%로 중기 추세는 아직 회복 전</t>
+        </is>
+      </c>
       <c r="E14" s="9" t="n">
         <v>0.6</v>
       </c>
@@ -5306,7 +5314,11 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>+0.2%, 1M -2.3·3M -2.9%로 17개 중 부진. 개선 신호 미확인</t>
+        </is>
+      </c>
       <c r="E15" s="9" t="n">
         <v>0.2</v>
       </c>
@@ -5378,7 +5390,11 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>-0.1%, 1M +0.2%로 정체. YTD26 +24.4% 5위로 연간 성과는 상위권 유지</t>
+        </is>
+      </c>
       <c r="E16" s="9" t="n">
         <v>-0.1</v>
       </c>
@@ -5678,7 +5694,11 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>-0.3%, 1주 +2.2%. YTD26 +23.9% 6위, 3M +2.3%로 모멘텀은 둔화</t>
+        </is>
+      </c>
       <c r="E20" s="9" t="n">
         <v>-0.3</v>
       </c>
@@ -5902,7 +5922,11 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>-0.1%, 3M -2.0%. 금리 상승 국면에서 배당 매력 희석 추정</t>
+        </is>
+      </c>
       <c r="E23" s="9" t="n">
         <v>-0.1</v>
       </c>
@@ -6050,7 +6074,11 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>0.0%, 1M +9.4%로 1M 상위이나 3M -8.5%로 17개 중 최하위권 — 방향 혼재</t>
+        </is>
+      </c>
       <c r="E25" s="9" t="n">
         <v>0</v>
       </c>
@@ -6122,7 +6150,11 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>+0.3%, 3M +9.6%. 아식스 신고가 등 소비 개별 강세는 있으나 섹터 확산은 제한적</t>
+        </is>
+      </c>
       <c r="E26" s="9" t="n">
         <v>0.3</v>
       </c>
@@ -6270,7 +6302,11 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>-0.6%, 1주 -1.7%로 은행(+3.1%)과 괴리. YTD26 +28.4% 4위는 유지</t>
+        </is>
+      </c>
       <c r="E28" s="9" t="n">
         <v>-0.6</v>
       </c>
